--- a/artfynd/A 60229-2025 artfynd.xlsx
+++ b/artfynd/A 60229-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5868,60 +5868,56 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135404127</v>
+        <v>135442281</v>
       </c>
       <c r="B51" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tjärnen på skogen, Dlr</t>
+          <t>Tjärnen i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446854</v>
+        <v>447021</v>
       </c>
       <c r="R51" t="n">
-        <v>6711084</v>
+        <v>6711241</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5948,90 +5944,100 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack. Foto finns i Avenza</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135404138</v>
+        <v>135442318</v>
       </c>
       <c r="B52" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tjärnen på skogen, Dlr</t>
+          <t>Tjärnen i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446872</v>
+        <v>447022</v>
       </c>
       <c r="R52" t="n">
-        <v>6711090</v>
+        <v>6711211</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6058,90 +6064,100 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack. Foto finns Avenza</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135404364</v>
+        <v>135442389</v>
       </c>
       <c r="B53" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tjärnen på skogen, Dlr</t>
+          <t>Tjärnen i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446840</v>
+        <v>447134</v>
       </c>
       <c r="R53" t="n">
-        <v>6711034</v>
+        <v>6711260</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6168,90 +6184,100 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135404373</v>
+        <v>135442450</v>
       </c>
       <c r="B54" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tjärnen på skogen, Dlr</t>
+          <t>Tjärnen i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446834</v>
+        <v>446923</v>
       </c>
       <c r="R54" t="n">
-        <v>6711030</v>
+        <v>6711176</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6278,90 +6304,100 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>ringhack. Foto finns i Avenza</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135404403</v>
+        <v>135442841</v>
       </c>
       <c r="B55" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjärnen på skogen, Dlr</t>
+          <t>Tjärnen i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446851</v>
+        <v>447036</v>
       </c>
       <c r="R55" t="n">
-        <v>6711029</v>
+        <v>6711103</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6388,90 +6424,100 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack. Hela trädet Båda sidor. Foton i Avenza</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135404478</v>
+        <v>135446053</v>
       </c>
       <c r="B56" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjärnen på skogen, Dlr</t>
+          <t>Tjärnen i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446841</v>
+        <v>447030</v>
       </c>
       <c r="R56" t="n">
-        <v>6710997</v>
+        <v>6711096</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6498,90 +6544,100 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska hack. Hela trädet</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135404896</v>
+        <v>135446063</v>
       </c>
       <c r="B57" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tjärnen på skogen, Dlr</t>
+          <t>Tjärnen i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447027</v>
+        <v>447016</v>
       </c>
       <c r="R57" t="n">
-        <v>6711119</v>
+        <v>6711136</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6608,90 +6664,100 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135404920</v>
+        <v>135446075</v>
       </c>
       <c r="B58" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tjärnen på skogen, Dlr</t>
+          <t>Tjärnen i skogen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447027</v>
+        <v>447007</v>
       </c>
       <c r="R58" t="n">
-        <v>6711115</v>
+        <v>6711157</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6718,37 +6784,51 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135404926</v>
+        <v>135404127</v>
       </c>
       <c r="B59" t="n">
         <v>99195</v>
@@ -6778,7 +6858,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6795,10 +6875,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447039</v>
+        <v>446854</v>
       </c>
       <c r="R59" t="n">
-        <v>6711101</v>
+        <v>6711084</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6858,7 +6938,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135404949</v>
+        <v>135404138</v>
       </c>
       <c r="B60" t="n">
         <v>99195</v>
@@ -6888,7 +6968,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6905,10 +6985,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447024</v>
+        <v>446872</v>
       </c>
       <c r="R60" t="n">
-        <v>6711094</v>
+        <v>6711090</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6968,7 +7048,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135405111</v>
+        <v>135404364</v>
       </c>
       <c r="B61" t="n">
         <v>99195</v>
@@ -6998,12 +7078,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -7015,10 +7095,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447135</v>
+        <v>446840</v>
       </c>
       <c r="R61" t="n">
-        <v>6711145</v>
+        <v>6711034</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7078,7 +7158,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135405308</v>
+        <v>135404373</v>
       </c>
       <c r="B62" t="n">
         <v>99195</v>
@@ -7108,7 +7188,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7125,10 +7205,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447145</v>
+        <v>446834</v>
       </c>
       <c r="R62" t="n">
-        <v>6711167</v>
+        <v>6711030</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7188,7 +7268,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135405364</v>
+        <v>135404403</v>
       </c>
       <c r="B63" t="n">
         <v>99195</v>
@@ -7218,12 +7298,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -7235,10 +7315,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447142</v>
+        <v>446851</v>
       </c>
       <c r="R63" t="n">
-        <v>6711196</v>
+        <v>6711029</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7298,37 +7378,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135404960</v>
+        <v>135404478</v>
       </c>
       <c r="B64" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7345,10 +7425,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447016</v>
+        <v>446841</v>
       </c>
       <c r="R64" t="n">
-        <v>6711099</v>
+        <v>6710997</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7408,37 +7488,46 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135404967</v>
+        <v>135404896</v>
       </c>
       <c r="B65" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7446,10 +7535,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447009</v>
+        <v>447027</v>
       </c>
       <c r="R65" t="n">
-        <v>6711104</v>
+        <v>6711119</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7506,6 +7595,1002 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135404920</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Tjärnen på skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>447027</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6711115</v>
+      </c>
+      <c r="S66" t="n">
+        <v>50</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Äppelbo</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135404926</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Tjärnen på skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>447039</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6711101</v>
+      </c>
+      <c r="S67" t="n">
+        <v>50</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Äppelbo</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135404949</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Tjärnen på skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>447024</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6711094</v>
+      </c>
+      <c r="S68" t="n">
+        <v>50</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Äppelbo</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135405111</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Tjärnen på skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>447135</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6711145</v>
+      </c>
+      <c r="S69" t="n">
+        <v>50</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Äppelbo</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135405308</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Tjärnen på skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>447145</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6711167</v>
+      </c>
+      <c r="S70" t="n">
+        <v>50</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Äppelbo</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135405364</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Tjärnen på skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>447142</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6711196</v>
+      </c>
+      <c r="S71" t="n">
+        <v>50</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Äppelbo</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135446092</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Tjärnen i skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>447002</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6711153</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Äppelbo</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Några m blomstestjälkar</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135404960</v>
+      </c>
+      <c r="B73" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Tjärnen på skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>447016</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6711099</v>
+      </c>
+      <c r="S73" t="n">
+        <v>50</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Äppelbo</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135404967</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Tjärnen på skogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>447009</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6711104</v>
+      </c>
+      <c r="S74" t="n">
+        <v>50</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Äppelbo</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60229-2025 artfynd.xlsx
+++ b/artfynd/A 60229-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404988</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405019</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405046</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404034</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404044</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404059</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404064</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404117</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404142</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404156</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404167</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1929,6 +1989,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404178</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2035,6 +2100,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404188</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2141,6 +2211,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404200</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2247,6 +2322,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404267</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2353,6 +2433,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404279</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2459,6 +2544,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404292</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2565,6 +2655,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404310</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2671,6 +2766,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404339</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2777,6 +2877,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404457</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2883,6 +2988,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404484</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2989,6 +3099,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404498</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3095,6 +3210,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404510</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3201,6 +3321,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404531</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3307,6 +3432,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404552</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3413,6 +3543,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404590</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3519,6 +3654,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404598</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3625,6 +3765,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404607</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3731,6 +3876,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404980</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3837,6 +3987,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405002</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3943,6 +4098,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405010</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4049,6 +4209,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405026</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4155,6 +4320,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405034</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4261,6 +4431,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405074</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4367,6 +4542,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405080</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4473,6 +4653,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405091</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4579,6 +4764,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405298</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4685,6 +4875,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405327</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4791,6 +4986,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405335</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4897,6 +5097,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405379</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5003,6 +5208,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405382</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5104,6 +5314,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404647</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5205,6 +5420,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405067</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5315,6 +5535,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405102</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5425,6 +5650,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404327</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5535,6 +5765,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404619</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5645,6 +5880,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404637</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5755,6 +5995,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404755</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5865,6 +6110,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405346</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5985,6 +6235,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442281</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6105,6 +6360,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442318</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6225,6 +6485,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442389</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6345,6 +6610,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442450</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6465,6 +6735,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442841</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6585,6 +6860,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446053</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6705,6 +6985,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446063</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6825,6 +7110,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446075</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6935,6 +7225,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404127</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7045,6 +7340,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404138</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7155,6 +7455,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404364</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7265,6 +7570,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404373</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7375,6 +7685,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404403</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7485,6 +7800,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404478</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7595,6 +7915,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404896</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7705,6 +8030,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404920</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7815,6 +8145,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404926</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7925,6 +8260,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404949</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8035,6 +8375,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405111</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8145,6 +8490,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405308</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8255,6 +8605,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405364</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8380,6 +8735,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446092</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8490,6 +8850,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404960</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8591,8 +8956,88 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 60229-2025 artfynd.xlsx
+++ b/artfynd/A 60229-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135404988</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135405019</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135405046</v>
       </c>
       <c r="B4" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135404034</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135404044</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135404059</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>135404064</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>135404117</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>135404142</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>135404156</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>135404167</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>135404178</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>135404188</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135404200</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>135404267</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135404279</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>135404292</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>135404310</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>135404339</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135404457</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>135404484</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>135404498</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>135404510</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>135404531</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>135404552</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>135404590</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135404598</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>135404607</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>135404980</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135405002</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>135405010</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>135405026</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>135405034</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>135405074</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>135405080</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>135405091</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135405298</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135405327</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>135405335</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>135405379</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>135405382</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>135404647</v>
       </c>
       <c r="B43" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>135405067</v>
       </c>
       <c r="B44" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>135405102</v>
       </c>
       <c r="B45" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>135404327</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>135404619</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135404637</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>135404755</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>135405346</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135442281</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>135442318</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>135442389</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>135442450</v>
       </c>
       <c r="B54" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>135442841</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>135446053</v>
       </c>
       <c r="B56" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>135446063</v>
       </c>
       <c r="B57" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>135446075</v>
       </c>
       <c r="B58" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>135404127</v>
       </c>
       <c r="B59" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>135404138</v>
       </c>
       <c r="B60" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>135404364</v>
       </c>
       <c r="B61" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>135404373</v>
       </c>
       <c r="B62" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135404403</v>
       </c>
       <c r="B63" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>135404478</v>
       </c>
       <c r="B64" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>135404896</v>
       </c>
       <c r="B65" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135404920</v>
       </c>
       <c r="B66" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>135404926</v>
       </c>
       <c r="B67" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>135404949</v>
       </c>
       <c r="B68" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>135405111</v>
       </c>
       <c r="B69" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>135405308</v>
       </c>
       <c r="B70" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>135405364</v>
       </c>
       <c r="B71" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>135446092</v>
       </c>
       <c r="B72" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135404960</v>
       </c>
       <c r="B73" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135404967</v>
       </c>
       <c r="B74" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 60229-2025 artfynd.xlsx
+++ b/artfynd/A 60229-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135404988</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135405019</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135405046</v>
       </c>
       <c r="B4" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135404034</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135404044</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135404059</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>135404064</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>135404117</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>135404142</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>135404156</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>135404167</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>135404178</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>135404188</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135404200</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>135404267</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135404279</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>135404292</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>135404310</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>135404339</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135404457</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>135404484</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>135404498</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>135404510</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>135404531</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>135404552</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>135404590</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135404598</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>135404607</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>135404980</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135405002</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>135405010</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>135405026</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>135405034</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>135405074</v>
       </c>
       <c r="B35" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>135405080</v>
       </c>
       <c r="B36" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>135405091</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135405298</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135405327</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>135405335</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>135405379</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>135405382</v>
       </c>
       <c r="B42" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>135404647</v>
       </c>
       <c r="B43" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>135405067</v>
       </c>
       <c r="B44" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>135404127</v>
       </c>
       <c r="B59" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>135404138</v>
       </c>
       <c r="B60" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>135404364</v>
       </c>
       <c r="B61" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>135404373</v>
       </c>
       <c r="B62" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135404403</v>
       </c>
       <c r="B63" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>135404478</v>
       </c>
       <c r="B64" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>135404896</v>
       </c>
       <c r="B65" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135404920</v>
       </c>
       <c r="B66" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>135404926</v>
       </c>
       <c r="B67" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>135404949</v>
       </c>
       <c r="B68" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>135405111</v>
       </c>
       <c r="B69" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>135405308</v>
       </c>
       <c r="B70" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>135405364</v>
       </c>
       <c r="B71" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>135446092</v>
       </c>
       <c r="B72" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135404960</v>
       </c>
       <c r="B73" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135404967</v>
       </c>
       <c r="B74" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 60229-2025 artfynd.xlsx
+++ b/artfynd/A 60229-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135404988</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135405019</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135405046</v>
       </c>
       <c r="B4" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>135404127</v>
       </c>
       <c r="B59" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>135404138</v>
       </c>
       <c r="B60" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>135404364</v>
       </c>
       <c r="B61" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>135404373</v>
       </c>
       <c r="B62" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135404403</v>
       </c>
       <c r="B63" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>135404478</v>
       </c>
       <c r="B64" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>135404896</v>
       </c>
       <c r="B65" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135404920</v>
       </c>
       <c r="B66" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>135404926</v>
       </c>
       <c r="B67" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>135404949</v>
       </c>
       <c r="B68" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>135405111</v>
       </c>
       <c r="B69" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>135405308</v>
       </c>
       <c r="B70" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>135405364</v>
       </c>
       <c r="B71" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>135446092</v>
       </c>
       <c r="B72" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135404960</v>
       </c>
       <c r="B73" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 60229-2025 artfynd.xlsx
+++ b/artfynd/A 60229-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135404988</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135405019</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135405046</v>
       </c>
       <c r="B4" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135404034</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135404044</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135404059</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>135404064</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>135404117</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>135404142</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>135404156</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>135404167</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>135404178</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>135404188</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135404200</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>135404267</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135404279</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>135404292</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>135404310</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>135404339</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135404457</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>135404484</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>135404498</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>135404510</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>135404531</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>135404552</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>135404590</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135404598</v>
       </c>
       <c r="B28" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>135404607</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>135404980</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135405002</v>
       </c>
       <c r="B31" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>135405010</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>135405026</v>
       </c>
       <c r="B33" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>135405034</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>135405074</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>135405080</v>
       </c>
       <c r="B36" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>135405091</v>
       </c>
       <c r="B37" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>135405298</v>
       </c>
       <c r="B38" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>135405327</v>
       </c>
       <c r="B39" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>135405335</v>
       </c>
       <c r="B40" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>135405379</v>
       </c>
       <c r="B41" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>135405382</v>
       </c>
       <c r="B42" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>135404647</v>
       </c>
       <c r="B43" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>135405067</v>
       </c>
       <c r="B44" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>135405102</v>
       </c>
       <c r="B45" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>135404327</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>135404619</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135404637</v>
       </c>
       <c r="B48" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>135404755</v>
       </c>
       <c r="B49" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>135405346</v>
       </c>
       <c r="B50" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135442281</v>
       </c>
       <c r="B51" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>135442318</v>
       </c>
       <c r="B52" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>135442389</v>
       </c>
       <c r="B53" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>135442450</v>
       </c>
       <c r="B54" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>135442841</v>
       </c>
       <c r="B55" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>135446053</v>
       </c>
       <c r="B56" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>135446063</v>
       </c>
       <c r="B57" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>135446075</v>
       </c>
       <c r="B58" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>135404127</v>
       </c>
       <c r="B59" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>135404138</v>
       </c>
       <c r="B60" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>135404364</v>
       </c>
       <c r="B61" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>135404373</v>
       </c>
       <c r="B62" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135404403</v>
       </c>
       <c r="B63" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>135404478</v>
       </c>
       <c r="B64" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>135404896</v>
       </c>
       <c r="B65" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135404920</v>
       </c>
       <c r="B66" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>135404926</v>
       </c>
       <c r="B67" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>135404949</v>
       </c>
       <c r="B68" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>135405111</v>
       </c>
       <c r="B69" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>135405308</v>
       </c>
       <c r="B70" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>135405364</v>
       </c>
       <c r="B71" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>135446092</v>
       </c>
       <c r="B72" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135404960</v>
       </c>
       <c r="B73" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135404967</v>
       </c>
       <c r="B74" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
